--- a/Assets/StreamingAssets/story/4.xlsx
+++ b/Assets/StreamingAssets/story/4.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\Resources\story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7049537D-CFAF-4B40-9451-58E4B45DB373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBB8334-7B0C-4A2F-A029-19403920BAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1550" windowWidth="20000" windowHeight="14450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11380" yWindow="1350" windowWidth="13280" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,12 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Dialogue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
+  <si>
+    <t>中文名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文对话「」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Avatar</t>
@@ -45,75 +47,200 @@
     <t>Bgm</t>
   </si>
   <si>
-    <t>Action1</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>Character1</t>
-  </si>
-  <si>
-    <t>Action2</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>Character2</t>
+    <t>CharacterCommands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English Name</t>
+  </si>
+  <si>
+    <t>English Dialogue</t>
+  </si>
+  <si>
+    <t>日本語名前</t>
+  </si>
+  <si>
+    <t>日本語会話</t>
+  </si>
+  <si>
+    <t>文化祭前夜，学校比平时安静。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">走廊尽头的圣诞树已经装饰好了。		
+彩灯一闪一闪，像某种不可靠的心跳。	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们把最后一批卡片挂上去。		
+白色的卡片在灯光下轻轻晃动。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每一张都写着别人没能说出口的话。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“谢谢你。”		
+“对不起。”		
+“圣诞节！！”		
+“如果可以的话....”		</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全是很普通的话。 
+可越普通，越让人难受。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Name]</t>
   </si>
   <si>
     <t>良治</t>
-  </si>
-  <si>
-    <t>appearAt</t>
-  </si>
-  <si>
-    <t>樱</t>
-  </si>
-  <si>
-    <t>好久不见。</t>
-  </si>
-  <si>
-    <t>moveTo</t>
-  </si>
-  <si>
-    <t>お久しぶり。</t>
-  </si>
-  <si>
-    <t>你怎么还和以前一样。</t>
-  </si>
-  <si>
-    <t>怎么了。</t>
-  </si>
-  <si>
-    <t>没事，我先走了。</t>
-  </si>
-  <si>
-    <t>disappear</t>
-  </si>
-  <si>
-    <t>LastBGlmg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastBGM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastX1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastX2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>end of story</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里是1-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Name]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「[Name]」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「嗯。」</t>
+  </si>
+  <si>
+    <t>「你会写什么？」</t>
+  </si>
+  <si>
+    <t>「不知道。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「又是不知道。」</t>
+  </si>
+  <si>
+    <t>「那你呢？」</t>
+  </si>
+  <si>
+    <t>「我已经写了。」</t>
+  </si>
+  <si>
+    <t>她指了指圣诞树最高处。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那里挂着一张没有名字的卡片。</t>
+  </si>
+  <si>
+    <t>「写了什么？」</t>
+  </si>
+  <si>
+    <t>「秘密。」</t>
+  </si>
+  <si>
+    <t>「匿名展示不是为了说真话吗？」</t>
+  </si>
+  <si>
+    <t>「是啊。」</t>
+  </si>
+  <si>
+    <t>「可是有些真话，就算匿名也说不出口。」</t>
+  </si>
+  <si>
+    <t>窗外忽然传来同学们的声音。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">我转过头。		
+雪落了。	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今年的第一场雪，比天气预报来得更早。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「下雪了。」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">靠得很近。 </t>
+  </si>
+  <si>
+    <t>却没有重叠。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们并肩站在窗前。 
+玻璃映出两个人的影子。 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「下学期我就要离开这里了。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「什么.....？」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「已经决定了。」</t>
+  </si>
+  <si>
+    <t>「本来不想说的。」</t>
+  </si>
+  <si>
+    <t>「可是如果不说，我们又会重复以前的事。」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我终于明白。		
+原来这几天不是开始。		
+是告别。		</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice</t>
+  </si>
+  <si>
+    <t>挽留桜
+问桜是否还喜欢自己
+沉默</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-1
+4-2
+4-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura:+50
+sakura:+50
+sakura:-50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1线150，2线50，三线-200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura:0,200
+sakura:-200,200
+sakura:-200,200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -121,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +262,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -157,9 +291,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -439,14 +582,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294B3738-0B50-4E27-88C2-74BD7B9AAF95}">
-  <dimension ref="A1:P9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="2" max="2" width="42.08203125" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,246 +625,324 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="N1" t="s">
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="O1" t="s">
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="P1" t="s">
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>-500</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3">
-        <v>-400</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3">
-        <v>800</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <f>IF(E2&lt;&gt;"",E2,M2)</f>
-        <v>2</v>
-      </c>
-      <c r="N3">
-        <f>IF(F2&lt;&gt;"",F2,N2)</f>
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <f>IF(H2&lt;&gt;"",H2,O2)</f>
-        <v>-500</v>
-      </c>
-      <c r="P3">
-        <f>IF(K2&lt;&gt;"",K2,P2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4">
-        <f t="shared" ref="M4:N8" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
-        <v>2</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <f t="shared" ref="O4:O8" si="1">IF(H3&lt;&gt;"",H3,O3)</f>
-        <v>-400</v>
-      </c>
-      <c r="P4">
-        <f t="shared" ref="P4:P8" si="2">IF(K3&lt;&gt;"",K3,P3)</f>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C14" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3"/>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3"/>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5">
-        <v>700</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>800</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>886</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8">
-        <v>-500</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="28" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="28" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
